--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488220_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488220_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8044</v>
+        <v>5.5717</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9541</v>
+        <v>4.3123</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8503</v>
+        <v>1.2593</v>
       </c>
       <c r="G2" t="n">
         <v>-0.213</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2594</v>
+        <v>2.0267</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7893</v>
+        <v>1.1475</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4701</v>
+        <v>0.8792</v>
       </c>
       <c r="V2" t="n">
         <v>2.8316</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.023</v>
+        <v>3.7255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7974</v>
+        <v>1.5491</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2256</v>
+        <v>2.1764</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6049</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2604</v>
+        <v>0.4421</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.1026</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5939</v>
+        <v>0.5446</v>
       </c>
       <c r="V3" t="n">
         <v>3.1471</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6884</v>
+        <v>2.3553</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1031</v>
+        <v>1.7454</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5853</v>
+        <v>0.6099</v>
       </c>
       <c r="G4" t="n">
         <v>2.2222</v>
@@ -766,13 +766,13 @@
         <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.1088</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4377</v>
+        <v>0.2046</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.338</v>
+        <v>-0.3134</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3139</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0506</v>
+        <v>1.1718</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2822</v>
+        <v>0.0296</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2316</v>
+        <v>1.1422</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4781</v>
+        <v>0.1501</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1985</v>
+        <v>-0.7393</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2796</v>
+        <v>0.8894</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1278</v>
+        <v>1.1681</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0863</v>
+        <v>-0.159</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0415</v>
+        <v>1.3271</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-1.018</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8878</v>
+        <v>-0.5803</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2381</v>
+        <v>-0.4377</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2597</v>
+        <v>0.0392</v>
       </c>
       <c r="T6" t="n">
-        <v>0.434</v>
+        <v>-0.0267</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6937</v>
+        <v>0.0659</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5733</v>
+        <v>-0.3144</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7872</v>
+        <v>0.6221</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3304</v>
+        <v>0.6221</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1176</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1501</v>
+        <v>0.6221</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7393</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8894</v>
+        <v>0.6221</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1681</v>
+        <v>0.6221</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.159</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3271</v>
+        <v>0.6221</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.018</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5803</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3454</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3867</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0413</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6221</v>
+        <v>0.6151</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6221</v>
+        <v>2.9452</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2.3301</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6221</v>
+        <v>0.4781</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.1985</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6221</v>
+        <v>0.2796</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6221</v>
+        <v>1.1278</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0863</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6221</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2381</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.7921</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4616</v>
+        <v>-0.1935</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7874</v>
+        <v>1.0063</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.249</v>
+        <v>-1.1997</v>
       </c>
       <c r="G9" t="n">
         <v>1.5843</v>
@@ -1156,13 +1156,13 @@
         <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2517</v>
+        <v>0.5198</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5061</v>
+        <v>0.725</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2545</v>
+        <v>-0.2052</v>
       </c>
       <c r="V9" t="n">
         <v>-0.63</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.025</v>
+        <v>-0.4866</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3212</v>
+        <v>-0.0044</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7038</v>
+        <v>-0.4822</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0986</v>
@@ -1234,13 +1234,13 @@
         <v>2.4087</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3907</v>
+        <v>0.1477</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2014</v>
+        <v>0.1154</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1893</v>
+        <v>0.0323</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.115</v>
+        <v>-0.9925</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2726</v>
+        <v>-0.1747</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8424</v>
+        <v>-0.8178</v>
       </c>
       <c r="G11" t="n">
         <v>0.7637</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9523</v>
+        <v>-0.8298</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8976</v>
+        <v>-0.873</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2514</v>
+        <v>-1.2042</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1852</v>
+        <v>0.9369</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4366</v>
+        <v>-2.1411</v>
       </c>
       <c r="G12" t="n">
         <v>-0.155</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4495</v>
+        <v>-0.4023</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4713</v>
+        <v>0.2804</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9782</v>
+        <v>-0.6827</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5733</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1608</v>
+        <v>-2.855</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5014</v>
+        <v>-2.294</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6594</v>
+        <v>-0.5609</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4535</v>
@@ -1468,13 +1468,13 @@
         <v>2.4087</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.2285</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2226</v>
+        <v>-0.0152</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1452</v>
+        <v>0.2437</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8888</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.5722</v>
+        <v>9.940000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9162</v>
+        <v>12.2841</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.344</v>
+        <v>-2.343999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3.9058</v>
@@ -1531,7 +1531,7 @@
         <v>-7.536100000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8557000000000001</v>
+        <v>-0.8556999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-6.6805</v>
@@ -1546,13 +1546,13 @@
         <v>16.6757</v>
       </c>
       <c r="S14" t="n">
-        <v>9.99999999999196e-05</v>
+        <v>1.368</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1007</v>
+        <v>2.468599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1008</v>
+        <v>-1.1007</v>
       </c>
       <c r="V14" t="n">
         <v>1.8872</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1783</v>
+        <v>5.3272</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9875</v>
+        <v>4.7916</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1908</v>
+        <v>0.5355</v>
       </c>
       <c r="G15" t="n">
         <v>4.8832</v>
@@ -1624,13 +1624,13 @@
         <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6879</v>
+        <v>-0.5391</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1044</v>
+        <v>-0.3003</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5835</v>
+        <v>-0.2388</v>
       </c>
       <c r="V15" t="n">
         <v>3.0212</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3236</v>
+        <v>0.4783</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7548</v>
+        <v>2.8528</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4312</v>
+        <v>-2.3745</v>
       </c>
       <c r="G16" t="n">
         <v>1.2482</v>
@@ -1702,13 +1702,13 @@
         <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.8086</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5931</v>
+        <v>-0.4952</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3701</v>
+        <v>-0.3134</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2583</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>M. MURILLO PONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2871</v>
+        <v>-0.0001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1741</v>
+        <v>-0.013</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.887</v>
+        <v>0.0129</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.3191</v>
+        <v>-1.0341</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.7632</v>
+        <v>-0.5118</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.556</v>
+        <v>-0.5223</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.2152</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.7282</v>
+        <v>0.0859</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.487</v>
+        <v>-0.6529</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.104</v>
+        <v>-0.4671</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.035</v>
+        <v>-0.5977</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.1306</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3441</v>
+        <v>0.4781</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0394</v>
+        <v>0.554</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3046</v>
+        <v>-0.0759</v>
       </c>
       <c r="V17" t="n">
-        <v>3.3357</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4616</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1408</v>
+        <v>-0.1696</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5902</v>
+        <v>1.1985</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4494</v>
+        <v>-1.368</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9827</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0117</v>
+        <v>0.7014</v>
       </c>
       <c r="T18" t="n">
-        <v>1.108</v>
+        <v>0.7163</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0963</v>
+        <v>-0.0149</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6294</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2902</v>
+        <v>-0.3394</v>
       </c>
       <c r="E19" t="n">
         <v>0.008200000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2984</v>
+        <v>-0.3477</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5348000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0555</v>
+        <v>0.0062</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1102</v>
+        <v>0.0609</v>
       </c>
       <c r="V19" t="n">
         <v>0.1891</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MURILLO PONS</t>
+          <t>R. ROMERO NARANJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5877</v>
+        <v>-0.8294</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6005</v>
+        <v>-0.7896</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0129</v>
+        <v>-0.0398</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0341</v>
+        <v>-0.3666</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5118</v>
+        <v>-0.6569</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5223</v>
+        <v>0.2903</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.4601</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0859</v>
+        <v>0.408</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6529</v>
+        <v>0.0522</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4671</v>
+        <v>-0.8267</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5977</v>
+        <v>-1.0648</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1306</v>
+        <v>0.2381</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2234</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1094</v>
+        <v>-0.1707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0336</v>
+        <v>-0.2851</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0759</v>
+        <v>0.1144</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8196</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4392</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. ROMERO NARANJO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-1.0112</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8875</v>
+        <v>-0.001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0152</v>
+        <v>-1.0101</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3666</v>
+        <v>-6.3191</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6569</v>
+        <v>-5.7632</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2903</v>
+        <v>-0.556</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4601</v>
+        <v>-3.2152</v>
       </c>
       <c r="K21" t="n">
-        <v>0.408</v>
+        <v>-2.7282</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0522</v>
+        <v>-0.487</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8267</v>
+        <v>-3.104</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0648</v>
+        <v>-3.035</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2381</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P21" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.1117</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.2234</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.244</v>
+        <v>1.0458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>0.8643</v>
       </c>
       <c r="U21" t="n">
-        <v>0.139</v>
+        <v>0.1815</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8196</v>
+        <v>3.3357</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>3.4616</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4392</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7112</v>
+        <v>-2.0625</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6406</v>
+        <v>0.9952</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0706</v>
+        <v>-3.0576</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8604</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9111</v>
+        <v>-2.3613</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9493</v>
+        <v>3.261</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1697</v>
+        <v>1.8248</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9488</v>
+        <v>-0.8293</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1185</v>
+        <v>2.6542</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6907</v>
+        <v>-0.9251</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8598</v>
+        <v>-1.532</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1692</v>
+        <v>0.6069</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2234</v>
+        <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7793</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4628</v>
+        <v>-0.0379</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2474</v>
+        <v>0.3774</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2154</v>
+        <v>-0.4154</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9439</v>
+        <v>-1.0714</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5722</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9439</v>
+        <v>-2.6436</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0268</v>
+        <v>-2.2136</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4076</v>
+        <v>-2.2489</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4344</v>
+        <v>0.0353</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8997000000000001</v>
+        <v>-1.8604</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3613</v>
+        <v>-0.9111</v>
       </c>
       <c r="I23" t="n">
-        <v>3.261</v>
+        <v>-0.9493</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8248</v>
+        <v>-0.1697</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8293</v>
+        <v>0.9488</v>
       </c>
       <c r="L23" t="n">
-        <v>2.6542</v>
+        <v>-1.1185</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9251</v>
+        <v>-1.6907</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.532</v>
+        <v>-1.8598</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6069</v>
+        <v>0.1692</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7793</v>
+        <v>-2.2234</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9264</v>
+        <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0023</v>
+        <v>0.0348</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2101</v>
+        <v>0.1443</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7921</v>
+        <v>-0.1095</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0714</v>
+        <v>-0.9439</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6436</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0935</v>
+        <v>-3.3059</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0437</v>
+        <v>-0.3375</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0498</v>
+        <v>-2.9685</v>
       </c>
       <c r="G24" t="n">
         <v>0.3738</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0679</v>
+        <v>-0.1446</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2151</v>
+        <v>-0.0786</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1473</v>
+        <v>-0.0659</v>
       </c>
       <c r="V24" t="n">
         <v>-4.091</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.89</v>
+        <v>-3.7931</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4061</v>
+        <v>-4.1123</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5161</v>
+        <v>0.3192</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2129</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0095</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6354</v>
+        <v>-0.3416</v>
       </c>
       <c r="U25" t="n">
-        <v>0.626</v>
+        <v>0.429</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.5723</v>
+        <v>-7.919299999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.344</v>
+        <v>2.343999999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.9162</v>
+        <v>-10.2633</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.9057</v>
+        <v>-3.905699999999999</v>
       </c>
       <c r="H26" t="n">
         <v>-12.738</v>
@@ -2458,10 +2458,10 @@
         <v>7.536</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8556999999999996</v>
+        <v>0.8556999999999998</v>
       </c>
       <c r="L26" t="n">
-        <v>6.6806</v>
+        <v>6.680599999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-11.4418</v>
@@ -2482,13 +2482,13 @@
         <v>13.8965</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0001000000000004279</v>
+        <v>0.6527999999999999</v>
       </c>
       <c r="T26" t="n">
         <v>1.1008</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1008</v>
+        <v>-0.448</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8873</v>
